--- a/kumu_1a.xlsx
+++ b/kumu_1a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/learath/Library/Mobile Documents/com~apple~CloudDocs/csp26/cs26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BACC22D-6512-4768-B5D3-0379D34BD72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B9F3EBB-79A5-4DB3-B52A-77CB13F76CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="32">
   <si>
     <t>Label</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>Auxiliary</t>
-  </si>
-  <si>
-    <t>defined as heat wave intensity considering 1. duration of a heat wave, 2. the heat waves average temperature, 3. amount of heat waves within one summer (?)</t>
   </si>
   <si>
     <t>VOI</t>
@@ -518,6 +515,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.95"/>
+  <cols>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.1">
       <c r="A1" t="s">
@@ -533,134 +533,170 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="56.1">
+    <row r="2" spans="1:4" ht="48">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.1">
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="12.75">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.1">
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12.75">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="166.5">
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="12.75">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="60">
+      <c r="A6" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="69.95">
-      <c r="A6" t="s">
-        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="56.1">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="48">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
       <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="72">
+      <c r="A8" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="84">
-      <c r="A8" t="s">
-        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
       <c r="D8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="36">
+      <c r="A9" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="42">
-      <c r="A9" t="s">
-        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="56.1">
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="48">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="48">
+      <c r="A11" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="69.95">
-      <c r="A11" t="s">
-        <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="69.95">
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="60">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
       <c r="D12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="24">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="27.95">
-      <c r="A13" t="s">
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="36">
+      <c r="A14" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="42">
-      <c r="A14" t="s">
-        <v>24</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="56.1">
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="48">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -675,13 +711,13 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.1">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -698,16 +734,16 @@
     </row>
     <row r="2" spans="1:7" ht="69.95">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="56.1">
@@ -715,44 +751,44 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="42">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="69.95">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="56.1">
@@ -760,78 +796,78 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="42">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27.95">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="56.1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.1">
@@ -842,10 +878,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="56.1">
@@ -856,58 +892,58 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="42">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="42">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="69.95">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="69.95">
@@ -915,13 +951,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="56.1">
@@ -929,55 +965,55 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="56.1">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="56.1">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="56.1">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.1">
@@ -985,16 +1021,16 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
